--- a/research/traditional_assets/database/data/thailand/thailand_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.102</v>
+        <v>0.0396</v>
       </c>
       <c r="E2">
-        <v>0.167</v>
+        <v>-0.0205</v>
       </c>
       <c r="G2">
-        <v>0.03951661631419939</v>
+        <v>0.08222996515679443</v>
       </c>
       <c r="H2">
-        <v>0.03951661631419939</v>
+        <v>0.08222996515679443</v>
       </c>
       <c r="I2">
-        <v>0.07563415225967055</v>
+        <v>0.06107267590727942</v>
       </c>
       <c r="J2">
-        <v>0.05418042452181712</v>
+        <v>0.04913016767835547</v>
       </c>
       <c r="K2">
-        <v>82.3</v>
+        <v>83.69000000000001</v>
       </c>
       <c r="L2">
-        <v>0.4972809667673716</v>
+        <v>0.583205574912892</v>
       </c>
       <c r="M2">
-        <v>55.84999999999999</v>
+        <v>54.26000000000001</v>
       </c>
       <c r="N2">
-        <v>0.02159789628369233</v>
+        <v>0.02791152263374486</v>
       </c>
       <c r="O2">
-        <v>0.6786148238153098</v>
+        <v>0.6483450830445692</v>
       </c>
       <c r="P2">
-        <v>55.84999999999999</v>
+        <v>54.26000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02159789628369233</v>
+        <v>0.02791152263374486</v>
       </c>
       <c r="R2">
-        <v>0.6786148238153098</v>
+        <v>0.6483450830445692</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>31.03</v>
+        <v>173.08</v>
       </c>
       <c r="V2">
-        <v>0.01199969062995476</v>
+        <v>0.08903292181069959</v>
       </c>
       <c r="W2">
-        <v>0.06118612203042214</v>
+        <v>0.06069387426547534</v>
       </c>
       <c r="X2">
-        <v>0.065302727779064</v>
+        <v>0.09984730564455246</v>
       </c>
       <c r="Y2">
-        <v>-0.004116605748641859</v>
+        <v>-0.03915343137907713</v>
       </c>
       <c r="Z2">
-        <v>0.04228294442453604</v>
+        <v>0.03780444079140183</v>
       </c>
       <c r="AA2">
-        <v>0.003729487825115545</v>
+        <v>0.002880639319253637</v>
       </c>
       <c r="AB2">
-        <v>0.05764704542872454</v>
+        <v>0.09066118876435159</v>
       </c>
       <c r="AC2">
-        <v>-0.05391755760360899</v>
+        <v>-0.08778054944509794</v>
       </c>
       <c r="AD2">
-        <v>2500.88</v>
+        <v>2319.26</v>
       </c>
       <c r="AE2">
-        <v>4.42773900512262</v>
+        <v>1.000355036527023</v>
       </c>
       <c r="AF2">
-        <v>2505.307739005123</v>
+        <v>2320.260355036527</v>
       </c>
       <c r="AG2">
-        <v>2474.277739005123</v>
+        <v>2147.180355036527</v>
       </c>
       <c r="AH2">
-        <v>0.4920851529611101</v>
+        <v>0.5441178919331373</v>
       </c>
       <c r="AI2">
-        <v>0.6393851391675613</v>
+        <v>0.6431838819232245</v>
       </c>
       <c r="AJ2">
-        <v>0.4889705197374329</v>
+        <v>0.5248315079517819</v>
       </c>
       <c r="AK2">
-        <v>0.636506549089124</v>
+        <v>0.62520167630463</v>
       </c>
       <c r="AL2">
-        <v>0.187</v>
+        <v>0.11</v>
       </c>
       <c r="AM2">
-        <v>0.034</v>
+        <v>-0.401</v>
       </c>
       <c r="AN2">
-        <v>198.4352931841625</v>
+        <v>280.9861885146595</v>
       </c>
       <c r="AO2">
-        <v>59.89304812834224</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AP2">
-        <v>196.3245051975817</v>
+        <v>260.1381578672796</v>
       </c>
       <c r="AQ2">
-        <v>329.4117647058823</v>
+        <v>-19.80049875311721</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.0675</v>
       </c>
       <c r="E3">
-        <v>0.117</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
-        <v>0.1513888888888889</v>
+        <v>0.367601246105919</v>
       </c>
       <c r="H3">
-        <v>0.1513888888888889</v>
+        <v>0.367601246105919</v>
       </c>
       <c r="I3">
-        <v>0.2592592592592592</v>
+        <v>0.2473520249221184</v>
       </c>
       <c r="J3">
-        <v>0.2092929292929293</v>
+        <v>0.1980711617192442</v>
       </c>
       <c r="K3">
-        <v>8.890000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="L3">
-        <v>0.205787037037037</v>
+        <v>0.1950155763239875</v>
       </c>
       <c r="M3">
-        <v>4.11</v>
+        <v>7.16</v>
       </c>
       <c r="N3">
-        <v>0.04155712841253792</v>
+        <v>0.08605769230769231</v>
       </c>
       <c r="O3">
-        <v>0.4623172103487064</v>
+        <v>1.143769968051118</v>
       </c>
       <c r="P3">
-        <v>4.11</v>
+        <v>7.16</v>
       </c>
       <c r="Q3">
-        <v>0.04155712841253792</v>
+        <v>0.08605769230769231</v>
       </c>
       <c r="R3">
-        <v>0.4623172103487064</v>
+        <v>1.143769968051118</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.33</v>
+        <v>7.08</v>
       </c>
       <c r="V3">
-        <v>0.06400404448938321</v>
+        <v>0.08509615384615385</v>
       </c>
       <c r="W3">
-        <v>0.2760869565217391</v>
+        <v>0.171978021978022</v>
       </c>
       <c r="X3">
-        <v>0.05616695310463903</v>
+        <v>0.08879860631824046</v>
       </c>
       <c r="Y3">
-        <v>0.2199200034171001</v>
+        <v>0.08317941565978151</v>
       </c>
       <c r="Z3">
-        <v>1.32759680393362</v>
+        <v>0.9742033383915022</v>
       </c>
       <c r="AA3">
-        <v>0.2778566240151981</v>
+        <v>0.1929615869859708</v>
       </c>
       <c r="AB3">
-        <v>0.0554136864023631</v>
+        <v>0.08823066852035569</v>
       </c>
       <c r="AC3">
-        <v>0.222442937612835</v>
+        <v>0.1047309184656151</v>
       </c>
       <c r="AD3">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="AG3">
-        <v>-3.45</v>
+        <v>-5.72</v>
       </c>
       <c r="AH3">
-        <v>0.02829632540774219</v>
+        <v>0.01608325449385052</v>
       </c>
       <c r="AI3">
-        <v>0.07331975560081466</v>
+        <v>0.04138770541692027</v>
       </c>
       <c r="AJ3">
-        <v>-0.03614457831325301</v>
+        <v>-0.07382550335570469</v>
       </c>
       <c r="AK3">
-        <v>-0.1047040971168437</v>
+        <v>-0.221877424359969</v>
       </c>
       <c r="AL3">
-        <v>0.187</v>
+        <v>0.11</v>
       </c>
       <c r="AM3">
-        <v>0.187</v>
+        <v>0.11</v>
       </c>
       <c r="AN3">
-        <v>0.2769230769230769</v>
+        <v>0.1881051175656985</v>
       </c>
       <c r="AO3">
-        <v>59.89304812834224</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AP3">
-        <v>-0.3317307692307692</v>
+        <v>-0.7911479944674965</v>
       </c>
       <c r="AQ3">
-        <v>59.89304812834224</v>
+        <v>72.18181818181819</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.095</v>
+        <v>0.0396</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,103 +865,100 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.04242034930721641</v>
+        <v>0.03475930414242032</v>
       </c>
       <c r="J4">
-        <v>0.02282986071806556</v>
+        <v>0.026834754967564</v>
       </c>
       <c r="K4">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="L4">
-        <v>0.05838709677419355</v>
+        <v>0.09398148148148147</v>
       </c>
       <c r="M4">
-        <v>2.44</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.006196038598273235</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.348066298342541</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>2.44</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.006196038598273235</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.348066298342541</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>22.4</v>
+        <v>16.7</v>
       </c>
       <c r="V4">
-        <v>0.0568816658202133</v>
+        <v>0.0435349322210636</v>
       </c>
       <c r="W4">
-        <v>0.01608888888888889</v>
+        <v>0.01884865366759517</v>
       </c>
       <c r="X4">
-        <v>0.065302727779064</v>
+        <v>0.09984730564455246</v>
       </c>
       <c r="Y4">
-        <v>-0.04921383889017511</v>
+        <v>-0.0809986519769573</v>
       </c>
       <c r="Z4">
-        <v>0.1633600778897593</v>
+        <v>0.1073473308303189</v>
       </c>
       <c r="AA4">
-        <v>0.003729487825115545</v>
+        <v>0.002880639319253637</v>
       </c>
       <c r="AB4">
-        <v>0.05764704542872454</v>
+        <v>0.09066118876435159</v>
       </c>
       <c r="AC4">
-        <v>-0.05391755760360899</v>
+        <v>-0.08778054944509794</v>
       </c>
       <c r="AD4">
-        <v>119.1</v>
+        <v>112.7</v>
       </c>
       <c r="AE4">
-        <v>4.424845857381458</v>
+        <v>0.9159951526186062</v>
       </c>
       <c r="AF4">
-        <v>123.5248458573815</v>
+        <v>113.6159951526186</v>
       </c>
       <c r="AG4">
-        <v>101.1248458573814</v>
+        <v>96.91599515261861</v>
       </c>
       <c r="AH4">
-        <v>0.2387761710007552</v>
+        <v>0.228504304487921</v>
       </c>
       <c r="AI4">
-        <v>0.4791037320185602</v>
+        <v>0.484057318201695</v>
       </c>
       <c r="AJ4">
-        <v>0.2043236396471431</v>
+        <v>0.2016915069015272</v>
       </c>
       <c r="AK4">
-        <v>0.4295419435833128</v>
+        <v>0.4445361684805472</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.153</v>
+        <v>-0.511</v>
       </c>
       <c r="AN4">
-        <v>54.13636363636363</v>
+        <v>120.6638115631692</v>
       </c>
       <c r="AP4">
-        <v>45.96583902608247</v>
+        <v>103.7644487715403</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -984,10 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.259</v>
+        <v>-0.158</v>
       </c>
       <c r="E5">
-        <v>0.217</v>
+        <v>-0.173</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,34 +993,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2.652103452100243e-05</v>
+        <v>0.0008143432429656645</v>
       </c>
       <c r="J5">
-        <v>2.131207712349915e-05</v>
+        <v>0.0006845204071305585</v>
       </c>
       <c r="K5">
-        <v>71.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L5">
-        <v>0.7842278203723987</v>
+        <v>0.8396436525612473</v>
       </c>
       <c r="M5">
-        <v>49.3</v>
+        <v>47.1</v>
       </c>
       <c r="N5">
-        <v>0.0235524555704185</v>
+        <v>0.03188464662875711</v>
       </c>
       <c r="O5">
-        <v>0.6885474860335196</v>
+        <v>0.6246684350132625</v>
       </c>
       <c r="P5">
-        <v>49.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q5">
-        <v>0.0235524555704185</v>
+        <v>0.03188464662875711</v>
       </c>
       <c r="R5">
-        <v>0.6885474860335196</v>
+        <v>0.6246684350132625</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,55 +1029,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>149.3</v>
       </c>
       <c r="V5">
-        <v>0.001098796101662526</v>
+        <v>0.101069591118332</v>
       </c>
       <c r="W5">
-        <v>0.06118612203042214</v>
+        <v>0.06069387426547534</v>
       </c>
       <c r="X5">
-        <v>0.09171977598308304</v>
+        <v>0.147096017944068</v>
       </c>
       <c r="Y5">
-        <v>-0.0305336539526609</v>
+        <v>-0.08640214367859264</v>
       </c>
       <c r="Z5">
-        <v>0.02473046439436394</v>
+        <v>0.02521279005277351</v>
       </c>
       <c r="AA5">
-        <v>5.270575644726339e-07</v>
+        <v>1.725866931182182e-05</v>
       </c>
       <c r="AB5">
-        <v>0.05864704292112388</v>
+        <v>0.0910370744986486</v>
       </c>
       <c r="AC5">
-        <v>-0.05864651586355941</v>
+        <v>-0.09101981582933678</v>
       </c>
       <c r="AD5">
-        <v>2378.9</v>
+        <v>2205.2</v>
       </c>
       <c r="AE5">
-        <v>0.002893147741162391</v>
+        <v>0.08435988390841663</v>
       </c>
       <c r="AF5">
-        <v>2378.902893147741</v>
+        <v>2205.284359883908</v>
       </c>
       <c r="AG5">
-        <v>2376.602893147741</v>
+        <v>2055.984359883908</v>
       </c>
       <c r="AH5">
-        <v>0.5319427906707493</v>
+        <v>0.5988577667586973</v>
       </c>
       <c r="AI5">
-        <v>0.6569372010746056</v>
+        <v>0.6602876394081387</v>
       </c>
       <c r="AJ5">
-        <v>0.5317019452448565</v>
+        <v>0.5819069005364506</v>
       </c>
       <c r="AK5">
-        <v>0.656719166918723</v>
+        <v>0.6443911609842896</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1089,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>792966.6666666666</v>
+        <v>24502.22222222222</v>
       </c>
       <c r="AP5">
-        <v>792200.9643825804</v>
+        <v>22844.27066537676</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0396</v>
+        <v>0.0111</v>
       </c>
       <c r="E2">
-        <v>-0.0205</v>
+        <v>-0.07907500000000001</v>
       </c>
       <c r="G2">
-        <v>0.08222996515679443</v>
+        <v>0.06179351921627732</v>
       </c>
       <c r="H2">
-        <v>0.08222996515679443</v>
+        <v>0.06179351921627732</v>
       </c>
       <c r="I2">
-        <v>0.06107267590727942</v>
+        <v>0.05139659367050033</v>
       </c>
       <c r="J2">
-        <v>0.04913016767835547</v>
+        <v>0.04503592068223673</v>
       </c>
       <c r="K2">
-        <v>83.69000000000001</v>
+        <v>55.79</v>
       </c>
       <c r="L2">
-        <v>0.583205574912892</v>
+        <v>0.420422004521477</v>
       </c>
       <c r="M2">
-        <v>54.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="N2">
-        <v>0.02791152263374486</v>
+        <v>0.04592720970537261</v>
       </c>
       <c r="O2">
-        <v>0.6483450830445692</v>
+        <v>0.9974905897114178</v>
       </c>
       <c r="P2">
-        <v>54.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="Q2">
-        <v>0.02791152263374486</v>
+        <v>0.04592720970537261</v>
       </c>
       <c r="R2">
-        <v>0.6483450830445692</v>
+        <v>0.9974905897114178</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>173.08</v>
+        <v>47.53</v>
       </c>
       <c r="V2">
-        <v>0.08903292181069959</v>
+        <v>0.03922588099364529</v>
       </c>
       <c r="W2">
-        <v>0.06069387426547534</v>
+        <v>0.04680063458487573</v>
       </c>
       <c r="X2">
-        <v>0.09984730564455246</v>
+        <v>0.08272471757493541</v>
       </c>
       <c r="Y2">
-        <v>-0.03915343137907713</v>
+        <v>-0.03592408299005968</v>
       </c>
       <c r="Z2">
-        <v>0.03780444079140183</v>
+        <v>0.03895158466438937</v>
       </c>
       <c r="AA2">
-        <v>0.002880639319253637</v>
+        <v>0.0007861363922785116</v>
       </c>
       <c r="AB2">
-        <v>0.09066118876435159</v>
+        <v>0.0751923074298714</v>
       </c>
       <c r="AC2">
-        <v>-0.08778054944509794</v>
+        <v>-0.07440617103759289</v>
       </c>
       <c r="AD2">
-        <v>2319.26</v>
+        <v>2578.41</v>
       </c>
       <c r="AE2">
-        <v>1.000355036527023</v>
+        <v>0.3433600996230333</v>
       </c>
       <c r="AF2">
-        <v>2320.260355036527</v>
+        <v>2578.753360099623</v>
       </c>
       <c r="AG2">
-        <v>2147.180355036527</v>
+        <v>2531.223360099622</v>
       </c>
       <c r="AH2">
-        <v>0.5441178919331373</v>
+        <v>0.6803284765999195</v>
       </c>
       <c r="AI2">
-        <v>0.6431838819232245</v>
+        <v>0.6590973011123258</v>
       </c>
       <c r="AJ2">
-        <v>0.5248315079517819</v>
+        <v>0.6762690861060674</v>
       </c>
       <c r="AK2">
-        <v>0.62520167630463</v>
+        <v>0.6549050611777878</v>
       </c>
       <c r="AL2">
-        <v>0.11</v>
+        <v>0.077</v>
       </c>
       <c r="AM2">
-        <v>-0.401</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AN2">
-        <v>280.9861885146595</v>
+        <v>365.265618359541</v>
       </c>
       <c r="AO2">
-        <v>72.18181818181819</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="AP2">
-        <v>260.1381578672796</v>
+        <v>358.581011488826</v>
       </c>
       <c r="AQ2">
-        <v>-19.80049875311721</v>
+        <v>-7.073954983922829</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0675</v>
+        <v>0.026</v>
       </c>
       <c r="E3">
-        <v>0.132</v>
+        <v>0.00485</v>
       </c>
       <c r="G3">
-        <v>0.367601246105919</v>
+        <v>0.2697368421052632</v>
       </c>
       <c r="H3">
-        <v>0.367601246105919</v>
+        <v>0.2697368421052632</v>
       </c>
       <c r="I3">
-        <v>0.2473520249221184</v>
+        <v>0.2171052631578947</v>
       </c>
       <c r="J3">
-        <v>0.1980711617192442</v>
+        <v>0.1751493380690991</v>
       </c>
       <c r="K3">
-        <v>6.26</v>
+        <v>5.27</v>
       </c>
       <c r="L3">
-        <v>0.1950155763239875</v>
+        <v>0.1733552631578947</v>
       </c>
       <c r="M3">
-        <v>7.16</v>
+        <v>5.15</v>
       </c>
       <c r="N3">
-        <v>0.08605769230769231</v>
+        <v>0.07006802721088436</v>
       </c>
       <c r="O3">
-        <v>1.143769968051118</v>
+        <v>0.9772296015180267</v>
       </c>
       <c r="P3">
-        <v>7.16</v>
+        <v>5.15</v>
       </c>
       <c r="Q3">
-        <v>0.08605769230769231</v>
+        <v>0.07006802721088436</v>
       </c>
       <c r="R3">
-        <v>1.143769968051118</v>
+        <v>0.9772296015180267</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.08</v>
+        <v>4.93</v>
       </c>
       <c r="V3">
-        <v>0.08509615384615385</v>
+        <v>0.06707482993197278</v>
       </c>
       <c r="W3">
-        <v>0.171978021978022</v>
+        <v>0.1673015873015873</v>
       </c>
       <c r="X3">
-        <v>0.08879860631824046</v>
+        <v>0.07626601330621802</v>
       </c>
       <c r="Y3">
-        <v>0.08317941565978151</v>
+        <v>0.09103557399536927</v>
       </c>
       <c r="Z3">
-        <v>0.9742033383915022</v>
+        <v>1.179208688906129</v>
       </c>
       <c r="AA3">
-        <v>0.1929615869859708</v>
+        <v>0.2065376213072387</v>
       </c>
       <c r="AB3">
-        <v>0.08823066852035569</v>
+        <v>0.07452513109988634</v>
       </c>
       <c r="AC3">
-        <v>0.1047309184656151</v>
+        <v>0.1320124902073523</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>5.21</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.36</v>
+        <v>5.21</v>
       </c>
       <c r="AG3">
-        <v>-5.72</v>
+        <v>0.2800000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.01608325449385052</v>
+        <v>0.06619235167068988</v>
       </c>
       <c r="AI3">
-        <v>0.04138770541692027</v>
+        <v>0.1400161246976619</v>
       </c>
       <c r="AJ3">
-        <v>-0.07382550335570469</v>
+        <v>0.003795066413662242</v>
       </c>
       <c r="AK3">
-        <v>-0.221877424359969</v>
+        <v>0.008674101610904593</v>
       </c>
       <c r="AL3">
-        <v>0.11</v>
+        <v>0.077</v>
       </c>
       <c r="AM3">
-        <v>0.11</v>
+        <v>0.077</v>
       </c>
       <c r="AN3">
-        <v>0.1881051175656985</v>
+        <v>0.7695716395864107</v>
       </c>
       <c r="AO3">
-        <v>72.18181818181819</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="AP3">
-        <v>-0.7911479944674965</v>
+        <v>0.04135893648449044</v>
       </c>
       <c r="AQ3">
-        <v>72.18181818181819</v>
+        <v>85.71428571428571</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0396</v>
+        <v>0.0111</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,100 +865,103 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.03475930414242032</v>
+        <v>0.007302688404458236</v>
       </c>
       <c r="J4">
-        <v>0.026834754967564</v>
+        <v>0.007302688404458236</v>
       </c>
       <c r="K4">
-        <v>2.03</v>
+        <v>-2.58</v>
       </c>
       <c r="L4">
-        <v>0.09398148148148147</v>
+        <v>-0.1258536585365854</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.005168661588683351</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>-0.7364341085271318</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.005168661588683351</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>-0.7364341085271318</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>16.7</v>
+        <v>19.6</v>
       </c>
       <c r="V4">
-        <v>0.0435349322210636</v>
+        <v>0.05331882480957563</v>
       </c>
       <c r="W4">
-        <v>0.01884865366759517</v>
+        <v>-0.02638036809815951</v>
       </c>
       <c r="X4">
-        <v>0.09984730564455246</v>
+        <v>0.08272471757493541</v>
       </c>
       <c r="Y4">
-        <v>-0.0809986519769573</v>
+        <v>-0.1091050856730949</v>
       </c>
       <c r="Z4">
-        <v>0.1073473308303189</v>
+        <v>0.1076502718914559</v>
       </c>
       <c r="AA4">
-        <v>0.002880639319253637</v>
+        <v>0.0007861363922785116</v>
       </c>
       <c r="AB4">
-        <v>0.09066118876435159</v>
+        <v>0.0751923074298714</v>
       </c>
       <c r="AC4">
-        <v>-0.08778054944509794</v>
+        <v>-0.07440617103759289</v>
       </c>
       <c r="AD4">
-        <v>112.7</v>
+        <v>109.5</v>
       </c>
       <c r="AE4">
-        <v>0.9159951526186062</v>
+        <v>0.261474438543031</v>
       </c>
       <c r="AF4">
-        <v>113.6159951526186</v>
+        <v>109.761474438543</v>
       </c>
       <c r="AG4">
-        <v>96.91599515261861</v>
+        <v>90.16147443854302</v>
       </c>
       <c r="AH4">
-        <v>0.228504304487921</v>
+        <v>0.2299336672856579</v>
       </c>
       <c r="AI4">
-        <v>0.484057318201695</v>
+        <v>0.475649042829179</v>
       </c>
       <c r="AJ4">
-        <v>0.2016915069015272</v>
+        <v>0.1969616917831029</v>
       </c>
       <c r="AK4">
-        <v>0.4445361684805472</v>
+        <v>0.4269788069924841</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.511</v>
+        <v>-1.01</v>
       </c>
       <c r="AN4">
-        <v>120.6638115631692</v>
+        <v>542.0792079207921</v>
       </c>
       <c r="AP4">
-        <v>103.7644487715403</v>
+        <v>446.3439328640744</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -981,10 +984,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.158</v>
+        <v>-0.0814</v>
       </c>
       <c r="E5">
-        <v>-0.173</v>
+        <v>-0.163</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0008143432429656645</v>
+        <v>0.000863360241858185</v>
       </c>
       <c r="J5">
-        <v>0.0006845204071305585</v>
+        <v>0.0007096660811558765</v>
       </c>
       <c r="K5">
-        <v>75.40000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="L5">
-        <v>0.8396436525612473</v>
+        <v>0.6491442542787287</v>
       </c>
       <c r="M5">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
       <c r="N5">
-        <v>0.03188464662875711</v>
+        <v>0.0630677394238256</v>
       </c>
       <c r="O5">
-        <v>0.6246684350132625</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="P5">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
       <c r="Q5">
-        <v>0.03188464662875711</v>
+        <v>0.0630677394238256</v>
       </c>
       <c r="R5">
-        <v>0.6246684350132625</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,55 +1032,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>149.3</v>
+        <v>23</v>
       </c>
       <c r="V5">
-        <v>0.101069591118332</v>
+        <v>0.02984687256683104</v>
       </c>
       <c r="W5">
-        <v>0.06069387426547534</v>
+        <v>0.04680063458487573</v>
       </c>
       <c r="X5">
-        <v>0.147096017944068</v>
+        <v>0.1649426143565915</v>
       </c>
       <c r="Y5">
-        <v>-0.08640214367859264</v>
+        <v>-0.1181419797717157</v>
       </c>
       <c r="Z5">
-        <v>0.02521279005277351</v>
+        <v>0.02563795662716592</v>
       </c>
       <c r="AA5">
-        <v>1.725866931182182e-05</v>
+        <v>1.819438820844517e-05</v>
       </c>
       <c r="AB5">
-        <v>0.0910370744986486</v>
+        <v>0.07735922242721507</v>
       </c>
       <c r="AC5">
-        <v>-0.09101981582933678</v>
+        <v>-0.07734102803900662</v>
       </c>
       <c r="AD5">
-        <v>2205.2</v>
+        <v>2463.7</v>
       </c>
       <c r="AE5">
-        <v>0.08435988390841663</v>
+        <v>0.08188566108000231</v>
       </c>
       <c r="AF5">
-        <v>2205.284359883908</v>
+        <v>2463.78188566108</v>
       </c>
       <c r="AG5">
-        <v>2055.984359883908</v>
+        <v>2440.78188566108</v>
       </c>
       <c r="AH5">
-        <v>0.5988577667586973</v>
+        <v>0.7617473671194223</v>
       </c>
       <c r="AI5">
-        <v>0.6602876394081387</v>
+        <v>0.6760122183985947</v>
       </c>
       <c r="AJ5">
-        <v>0.5819069005364506</v>
+        <v>0.7600409956097862</v>
       </c>
       <c r="AK5">
-        <v>0.6443911609842896</v>
+        <v>0.6739546316279252</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1086,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>24502.22222222222</v>
+        <v>28318.3908045977</v>
       </c>
       <c r="AP5">
-        <v>22844.27066537676</v>
+        <v>28054.96420300092</v>
       </c>
     </row>
   </sheetData>
